--- a/Costo obras al 17-06-26 (1) (1).xlsx
+++ b/Costo obras al 17-06-26 (1) (1).xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mvaceros-my.sharepoint.com/personal/analista2_metalurgicavera_com_py1/Documents/Yennifer Mancuello/1-LINK Y FORMATO REPORTE COSTO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2049F895-E094-4F20-87DB-AAA442D15886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="8_{2049F895-E094-4F20-87DB-AAA442D15886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8761523-D2C5-4653-AE03-9F0574FEFE01}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="m" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">m!$A$1:$AI$244</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">m!$A$1:$AF$244</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="290">
   <si>
     <t xml:space="preserve">Nro. OT </t>
   </si>
@@ -847,19 +847,61 @@
     <t>Adicional - REM - E.M. - PAREDES EDIFICIO HORNO</t>
   </si>
   <si>
-    <t>25560</t>
-  </si>
-  <si>
-    <t>25730</t>
+    <t>TECHO VIVIENDA DOS SANTOS OPC N° 2</t>
+  </si>
+  <si>
+    <t>Parasol_Edif. First Mariscal</t>
+  </si>
+  <si>
+    <t>LPI 1844/24 OBRAS PRELIMINARES ACARAY</t>
+  </si>
+  <si>
+    <t>Escalera Marinera - Parglass</t>
+  </si>
+  <si>
+    <t>Mano de Obra - Galpón Aratiri</t>
+  </si>
+  <si>
+    <t>San Ramon - Arq. Maria Rehnfeldt</t>
+  </si>
+  <si>
+    <t>Adicional - Ziplan / Canaleta Opción Zipada - PARG</t>
+  </si>
+  <si>
+    <t>Galpón N°3 30x90, Puerto Seguro</t>
+  </si>
+  <si>
+    <t>Proyecto REM - E.M. - PAREDES EDIFICIO HORNO</t>
+  </si>
+  <si>
+    <t>Adecuación Zona Trampolines</t>
+  </si>
+  <si>
+    <t>Bauleras Amplación</t>
+  </si>
+  <si>
+    <t>CPP-FPTI-PY-024-2024 - Estructuras Metálicas</t>
+  </si>
+  <si>
+    <t>Techo Club House Golf</t>
+  </si>
+  <si>
+    <t>Nave de Producción PARGLASS Opc 2</t>
+  </si>
+  <si>
+    <t>Puentes Peatonales y Ascensores Panorómicos con riostras R3 Victoria Rigia DP</t>
+  </si>
+  <si>
+    <t>Siderurgica Las Lomas</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="171" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -926,7 +968,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -999,6 +1041,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1027,7 +1075,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1089,26 +1137,53 @@
     <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="4" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF3E"/>
-          <bgColor rgb="FF000000"/>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1489,9 +1564,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:AF245"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AF260"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.140625" customWidth="1"/>
@@ -1621,7 +1695,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="23">
         <v>1</v>
       </c>
@@ -1716,7 +1790,7 @@
         <v>6.5647721786003296E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="23">
         <v>2</v>
       </c>
@@ -1811,7 +1885,7 @@
         <v>0.60941531085824718</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="23">
         <v>3</v>
       </c>
@@ -1907,7 +1981,7 @@
         <v>0.93908015171267079</v>
       </c>
     </row>
-    <row r="5" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="23">
         <v>4</v>
       </c>
@@ -2097,7 +2171,7 @@
         <v>0.87767854607493578</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="23">
         <v>6</v>
       </c>
@@ -2192,9 +2266,9 @@
         <v>1.0903843983968078</v>
       </c>
     </row>
-    <row r="8" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="16">
         <v>30903</v>
@@ -2289,7 +2363,7 @@
     </row>
     <row r="9" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="13">
         <v>30936</v>
@@ -2382,9 +2456,9 @@
         <v>0.91355903716022402</v>
       </c>
     </row>
-    <row r="10" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="23">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B10" s="13">
         <v>30980</v>
@@ -2477,9 +2551,9 @@
         <v>1.011248583474329</v>
       </c>
     </row>
-    <row r="11" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="23">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B11" s="16">
         <v>30984</v>
@@ -2572,9 +2646,9 @@
         <v>0.11120966148454145</v>
       </c>
     </row>
-    <row r="12" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="23">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B12" s="13">
         <v>31182</v>
@@ -2667,9 +2741,9 @@
         <v>1.3244127391573774</v>
       </c>
     </row>
-    <row r="13" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="23">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B13" s="16">
         <v>31183</v>
@@ -2762,9 +2836,9 @@
         <v>0.21023357374295124</v>
       </c>
     </row>
-    <row r="14" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="23">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B14" s="13">
         <v>31184</v>
@@ -2857,9 +2931,9 @@
         <v>6.2146849527974987E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="23">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B15" s="16">
         <v>31185</v>
@@ -2952,9 +3026,9 @@
         <v>0.18723904652863041</v>
       </c>
     </row>
-    <row r="16" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="23">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B16" s="13">
         <v>31186</v>
@@ -3047,9 +3121,9 @@
         <v>1.4591172681079876</v>
       </c>
     </row>
-    <row r="17" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="23">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B17" s="16">
         <v>31195</v>
@@ -3142,9 +3216,9 @@
         <v>2.2972258760410966E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="23">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B18" s="13">
         <v>31207</v>
@@ -3237,9 +3311,9 @@
         <v>0.34741827761981114</v>
       </c>
     </row>
-    <row r="19" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="23">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B19" s="13">
         <v>31232</v>
@@ -3332,9 +3406,9 @@
         <v>1.1946135988357254</v>
       </c>
     </row>
-    <row r="20" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="23">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B20" s="16">
         <v>31242</v>
@@ -3427,9 +3501,9 @@
         <v>0.70270223843477964</v>
       </c>
     </row>
-    <row r="21" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="23">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B21" s="13">
         <v>31245</v>
@@ -3524,7 +3598,7 @@
     </row>
     <row r="22" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="23">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B22" s="13">
         <v>31297</v>
@@ -3617,9 +3691,9 @@
         <v>0.80914456188829786</v>
       </c>
     </row>
-    <row r="23" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="23">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="B23" s="13">
         <v>31313</v>
@@ -3712,9 +3786,9 @@
         <v>0.72173094681116923</v>
       </c>
     </row>
-    <row r="24" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="23">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B24" s="16">
         <v>31341</v>
@@ -3807,9 +3881,9 @@
         <v>1.1278008508549553</v>
       </c>
     </row>
-    <row r="25" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="23">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B25" s="13">
         <v>31350</v>
@@ -3902,9 +3976,9 @@
         <v>1.4979689963760883</v>
       </c>
     </row>
-    <row r="26" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="23">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B26" s="16">
         <v>31356</v>
@@ -3997,9 +4071,9 @@
         <v>4.6602425948518815E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="23">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B27" s="13">
         <v>31374</v>
@@ -4092,9 +4166,9 @@
         <v>0.50194624390239639</v>
       </c>
     </row>
-    <row r="28" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="23">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="B28" s="16">
         <v>31368</v>
@@ -4187,9 +4261,9 @@
         <v>2.1965097501129356</v>
       </c>
     </row>
-    <row r="29" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="23">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B29" s="13">
         <v>31370</v>
@@ -4284,7 +4358,7 @@
     </row>
     <row r="30" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="23">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B30" s="16">
         <v>31373</v>
@@ -4377,9 +4451,9 @@
         <v>0.85565826287361701</v>
       </c>
     </row>
-    <row r="31" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="23">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="B31" s="16">
         <v>31421</v>
@@ -4473,9 +4547,9 @@
         <v>4.8676365871948048E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="23">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="B32" s="13">
         <v>31419</v>
@@ -4568,9 +4642,9 @@
         <v>0.20411995675286465</v>
       </c>
     </row>
-    <row r="33" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="23">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="B33" s="13">
         <v>31424</v>
@@ -4663,9 +4737,9 @@
         <v>1.2371165886477049</v>
       </c>
     </row>
-    <row r="34" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="23">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="B34" s="16">
         <v>31423</v>
@@ -4758,9 +4832,9 @@
         <v>1.6024507110777748</v>
       </c>
     </row>
-    <row r="35" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="23">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="B35" s="16">
         <v>31434</v>
@@ -4853,9 +4927,9 @@
         <v>0.59422956315621167</v>
       </c>
     </row>
-    <row r="36" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="23">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="B36" s="16">
         <v>31438</v>
@@ -4948,9 +5022,9 @@
         <v>1.846190112650008</v>
       </c>
     </row>
-    <row r="37" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="23">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="B37" s="13">
         <v>31445</v>
@@ -5043,9 +5117,9 @@
         <v>0.6207807810178495</v>
       </c>
     </row>
-    <row r="38" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="23">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="B38" s="16">
         <v>31442</v>
@@ -5138,9 +5212,9 @@
         <v>0.45990977807932892</v>
       </c>
     </row>
-    <row r="39" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="23">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="B39" s="13">
         <v>31455</v>
@@ -5234,9 +5308,9 @@
         <v>3.7045498292084575E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="23">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="B40" s="16">
         <v>31456</v>
@@ -5330,9 +5404,9 @@
         <v>4.0159894509630097E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="23">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="B41" s="13">
         <v>31476</v>
@@ -5426,9 +5500,9 @@
         <v>0.4043574361333333</v>
       </c>
     </row>
-    <row r="42" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="23">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="B42" s="16">
         <v>31479</v>
@@ -5521,9 +5595,9 @@
         <v>3.4185916101978318E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="23">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="B43" s="16">
         <v>31484</v>
@@ -5616,9 +5690,9 @@
         <v>0.40027405688672374</v>
       </c>
     </row>
-    <row r="44" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="23">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="B44" s="13">
         <v>31483</v>
@@ -5711,9 +5785,9 @@
         <v>0.28285807613742031</v>
       </c>
     </row>
-    <row r="45" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="23">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="B45" s="13">
         <v>31503</v>
@@ -5806,9 +5880,9 @@
         <v>0.62915655114058355</v>
       </c>
     </row>
-    <row r="46" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="23">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="B46" s="16">
         <v>31508</v>
@@ -5901,9 +5975,9 @@
         <v>6.6816964597557552E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="23">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="B47" s="16">
         <v>31507</v>
@@ -5996,9 +6070,9 @@
         <v>1.9626235605711235</v>
       </c>
     </row>
-    <row r="48" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="23">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="B48" s="16">
         <v>31525</v>
@@ -6091,9 +6165,9 @@
         <v>0.11035175710892095</v>
       </c>
     </row>
-    <row r="49" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="23">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="B49" s="13">
         <v>31527</v>
@@ -6186,9 +6260,9 @@
         <v>3.5644963388655596E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="23">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="B50" s="16">
         <v>31534</v>
@@ -6281,9 +6355,9 @@
         <v>0.54635304289709563</v>
       </c>
     </row>
-    <row r="51" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="23">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="B51" s="13">
         <v>31531</v>
@@ -6378,7 +6452,7 @@
     </row>
     <row r="52" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="23">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="B52" s="16">
         <v>31521</v>
@@ -6471,9 +6545,9 @@
         <v>0.90832369152672687</v>
       </c>
     </row>
-    <row r="53" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="23">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="B53" s="13">
         <v>31522</v>
@@ -6568,7 +6642,7 @@
     </row>
     <row r="54" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="23">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="B54" s="16">
         <v>31546</v>
@@ -6661,9 +6735,9 @@
         <v>0.80094016413330449</v>
       </c>
     </row>
-    <row r="55" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="23">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="B55" s="13">
         <v>31552</v>
@@ -6756,9 +6830,9 @@
         <v>0.10004194267666666</v>
       </c>
     </row>
-    <row r="56" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="23">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="B56" s="16">
         <v>31551</v>
@@ -6851,9 +6925,9 @@
         <v>0.27005953418203504</v>
       </c>
     </row>
-    <row r="57" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="23">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="B57" s="16">
         <v>31567</v>
@@ -6946,9 +7020,9 @@
         <v>0.12549424547001933</v>
       </c>
     </row>
-    <row r="58" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="23">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="B58" s="13">
         <v>31568</v>
@@ -7041,9 +7115,9 @@
         <v>0.17189244412293539</v>
       </c>
     </row>
-    <row r="59" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="23">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="B59" s="16">
         <v>31575</v>
@@ -7136,9 +7210,9 @@
         <v>4.1085030129136398E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="23">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="B60" s="13">
         <v>31579</v>
@@ -7233,7 +7307,7 @@
     </row>
     <row r="61" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="23">
-        <v>99</v>
+        <v>60</v>
       </c>
       <c r="B61" s="13">
         <v>31581</v>
@@ -7328,7 +7402,7 @@
     </row>
     <row r="62" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="23">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="B62" s="16">
         <v>31585</v>
@@ -7421,9 +7495,9 @@
         <v>0.84503516026991432</v>
       </c>
     </row>
-    <row r="63" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="23">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="B63" s="13">
         <v>31595</v>
@@ -7516,9 +7590,9 @@
         <v>0.32673495912865208</v>
       </c>
     </row>
-    <row r="64" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="23">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="B64" s="16">
         <v>31596</v>
@@ -7611,9 +7685,9 @@
         <v>0.41323961345758037</v>
       </c>
     </row>
-    <row r="65" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="23">
-        <v>103</v>
+        <v>64</v>
       </c>
       <c r="B65" s="13">
         <v>31601</v>
@@ -7706,9 +7780,9 @@
         <v>23.95335714315414</v>
       </c>
     </row>
-    <row r="66" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="23">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="B66" s="16">
         <v>31605</v>
@@ -7801,9 +7875,9 @@
         <v>1.3387886122808814</v>
       </c>
     </row>
-    <row r="67" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="23">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="B67" s="13">
         <v>31620</v>
@@ -7896,9 +7970,9 @@
         <v>1.371067291367607</v>
       </c>
     </row>
-    <row r="68" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="23">
-        <v>106</v>
+        <v>67</v>
       </c>
       <c r="B68" s="16">
         <v>31616</v>
@@ -7993,7 +8067,7 @@
     </row>
     <row r="69" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="23">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="B69" s="13">
         <v>31627</v>
@@ -8086,9 +8160,9 @@
         <v>0.75748605355377452</v>
       </c>
     </row>
-    <row r="70" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="23">
-        <v>110</v>
+        <v>69</v>
       </c>
       <c r="B70" s="16">
         <v>31628</v>
@@ -8181,9 +8255,9 @@
         <v>0.10035497869658874</v>
       </c>
     </row>
-    <row r="71" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="23">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="B71" s="16">
         <v>31656</v>
@@ -8276,9 +8350,9 @@
         <v>0.6679305940984237</v>
       </c>
     </row>
-    <row r="72" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="23">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="B72" s="13">
         <v>31667</v>
@@ -8371,9 +8445,9 @@
         <v>1.3942379560125588</v>
       </c>
     </row>
-    <row r="73" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="23">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="B73" s="16">
         <v>31675</v>
@@ -8466,9 +8540,9 @@
         <v>4.0413330426866879E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="23">
-        <v>124</v>
+        <v>73</v>
       </c>
       <c r="B74" s="16">
         <v>31680</v>
@@ -8561,9 +8635,9 @@
         <v>6.9599757140493684E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="23">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="B75" s="13">
         <v>31695</v>
@@ -8656,9 +8730,9 @@
         <v>0.68447496163033239</v>
       </c>
     </row>
-    <row r="76" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="23">
-        <v>127</v>
+        <v>75</v>
       </c>
       <c r="B76" s="13">
         <v>31692</v>
@@ -8751,9 +8825,9 @@
         <v>2.593021620225</v>
       </c>
     </row>
-    <row r="77" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="23">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="B77" s="16">
         <v>31696</v>
@@ -8846,9 +8920,9 @@
         <v>0.25670498385398488</v>
       </c>
     </row>
-    <row r="78" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="23">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="B78" s="13">
         <v>31709</v>
@@ -8943,7 +9017,7 @@
     </row>
     <row r="79" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="23">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="B79" s="16">
         <v>31721</v>
@@ -9036,9 +9110,9 @@
         <v>0.9297986286824178</v>
       </c>
     </row>
-    <row r="80" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="23">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="B80" s="16">
         <v>31733</v>
@@ -9131,9 +9205,9 @@
         <v>0.22233806128781874</v>
       </c>
     </row>
-    <row r="81" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="23">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="B81" s="13">
         <v>31724</v>
@@ -9226,9 +9300,9 @@
         <v>0.66501871013465019</v>
       </c>
     </row>
-    <row r="82" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="23">
-        <v>136</v>
+        <v>81</v>
       </c>
       <c r="B82" s="16">
         <v>31734</v>
@@ -9321,9 +9395,9 @@
         <v>0.69556068916565605</v>
       </c>
     </row>
-    <row r="83" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="23">
-        <v>137</v>
+        <v>82</v>
       </c>
       <c r="B83" s="13">
         <v>31745</v>
@@ -9414,9 +9488,9 @@
       </c>
       <c r="AE83" s="17"/>
     </row>
-    <row r="84" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="23">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="B84" s="16">
         <v>31760</v>
@@ -9509,9 +9583,9 @@
         <v>9.3730355714582936E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="23">
-        <v>143</v>
+        <v>84</v>
       </c>
       <c r="B85" s="13">
         <v>31756</v>
@@ -9604,9 +9678,9 @@
         <v>8.0067269463169027E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="23">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="B86" s="16">
         <v>31759</v>
@@ -9699,9 +9773,9 @@
         <v>1.0480446430891235</v>
       </c>
     </row>
-    <row r="87" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="23">
-        <v>145</v>
+        <v>86</v>
       </c>
       <c r="B87" s="13">
         <v>31766</v>
@@ -9794,9 +9868,9 @@
         <v>1.1568833422071458</v>
       </c>
     </row>
-    <row r="88" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="23">
-        <v>146</v>
+        <v>87</v>
       </c>
       <c r="B88" s="16">
         <v>31763</v>
@@ -9889,9 +9963,9 @@
         <v>6.7059470536045112</v>
       </c>
     </row>
-    <row r="89" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="23">
-        <v>147</v>
+        <v>88</v>
       </c>
       <c r="B89" s="13">
         <v>31765</v>
@@ -9984,9 +10058,9 @@
         <v>0.63959616301476296</v>
       </c>
     </row>
-    <row r="90" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="23">
-        <v>148</v>
+        <v>89</v>
       </c>
       <c r="B90" s="16">
         <v>31770</v>
@@ -10079,9 +10153,9 @@
         <v>1.8435406255808013</v>
       </c>
     </row>
-    <row r="91" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="23">
-        <v>149</v>
+        <v>90</v>
       </c>
       <c r="B91" s="13">
         <v>31777</v>
@@ -10174,9 +10248,9 @@
         <v>0.21927410165339861</v>
       </c>
     </row>
-    <row r="92" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="23">
-        <v>150</v>
+        <v>91</v>
       </c>
       <c r="B92" s="16">
         <v>31771</v>
@@ -10269,9 +10343,9 @@
         <v>0.11776254851975933</v>
       </c>
     </row>
-    <row r="93" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="23">
-        <v>151</v>
+        <v>92</v>
       </c>
       <c r="B93" s="13">
         <v>31775</v>
@@ -10364,9 +10438,9 @@
         <v>0.58479814793917162</v>
       </c>
     </row>
-    <row r="94" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="23">
-        <v>152</v>
+        <v>93</v>
       </c>
       <c r="B94" s="16">
         <v>31772</v>
@@ -10459,9 +10533,9 @@
         <v>0.14177691501063833</v>
       </c>
     </row>
-    <row r="95" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="23">
-        <v>154</v>
+        <v>94</v>
       </c>
       <c r="B95" s="16">
         <v>31789</v>
@@ -10554,9 +10628,9 @@
         <v>9.3350073478806903E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="23">
-        <v>155</v>
+        <v>95</v>
       </c>
       <c r="B96" s="13">
         <v>31787</v>
@@ -10649,9 +10723,9 @@
         <v>0.141197659597076</v>
       </c>
     </row>
-    <row r="97" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="23">
-        <v>156</v>
+        <v>96</v>
       </c>
       <c r="B97" s="16">
         <v>31793</v>
@@ -10744,9 +10818,9 @@
         <v>1.9264647073106105</v>
       </c>
     </row>
-    <row r="98" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="23">
-        <v>157</v>
+        <v>97</v>
       </c>
       <c r="B98" s="13">
         <v>31801</v>
@@ -10839,9 +10913,9 @@
         <v>1.8797735537883489</v>
       </c>
     </row>
-    <row r="99" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="23">
-        <v>160</v>
+        <v>98</v>
       </c>
       <c r="B99" s="16">
         <v>31803</v>
@@ -10934,9 +11008,9 @@
         <v>0.33211878480472401</v>
       </c>
     </row>
-    <row r="100" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="23">
-        <v>161</v>
+        <v>99</v>
       </c>
       <c r="B100" s="13">
         <v>31808</v>
@@ -11029,9 +11103,9 @@
         <v>1.0427368224192974</v>
       </c>
     </row>
-    <row r="101" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="23">
-        <v>163</v>
+        <v>100</v>
       </c>
       <c r="B101" s="13">
         <v>31810</v>
@@ -11126,7 +11200,7 @@
     </row>
     <row r="102" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="23">
-        <v>164</v>
+        <v>101</v>
       </c>
       <c r="B102" s="16">
         <v>31824</v>
@@ -11219,9 +11293,9 @@
         <v>0.78191301510282962</v>
       </c>
     </row>
-    <row r="103" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="23">
-        <v>165</v>
+        <v>102</v>
       </c>
       <c r="B103" s="13">
         <v>31821</v>
@@ -11314,9 +11388,9 @@
         <v>1.9808659963563866</v>
       </c>
     </row>
-    <row r="104" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="23">
-        <v>166</v>
+        <v>103</v>
       </c>
       <c r="B104" s="16">
         <v>31829</v>
@@ -11409,9 +11483,9 @@
         <v>2.3759119858763751</v>
       </c>
     </row>
-    <row r="105" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="23">
-        <v>167</v>
+        <v>104</v>
       </c>
       <c r="B105" s="13">
         <v>31830</v>
@@ -11504,9 +11578,9 @@
         <v>0.55261195711658018</v>
       </c>
     </row>
-    <row r="106" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="23">
-        <v>169</v>
+        <v>105</v>
       </c>
       <c r="B106" s="13">
         <v>31819</v>
@@ -11599,9 +11673,9 @@
         <v>0.22927362901071444</v>
       </c>
     </row>
-    <row r="107" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="23">
-        <v>170</v>
+        <v>106</v>
       </c>
       <c r="B107" s="16">
         <v>31831</v>
@@ -11694,9 +11768,9 @@
         <v>2.8272305446153844E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="23">
-        <v>172</v>
+        <v>107</v>
       </c>
       <c r="B108" s="16">
         <v>31838</v>
@@ -11789,9 +11863,9 @@
         <v>0.20255843548249877</v>
       </c>
     </row>
-    <row r="109" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="23">
-        <v>175</v>
+        <v>108</v>
       </c>
       <c r="B109" s="13">
         <v>31832</v>
@@ -11884,9 +11958,9 @@
         <v>0.35766150948911579</v>
       </c>
     </row>
-    <row r="110" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="23">
-        <v>176</v>
+        <v>109</v>
       </c>
       <c r="B110" s="16">
         <v>31846</v>
@@ -11981,7 +12055,7 @@
     </row>
     <row r="111" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="23">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="B111" s="16">
         <v>31852</v>
@@ -12074,9 +12148,9 @@
         <v>0.80159905523292818</v>
       </c>
     </row>
-    <row r="112" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="23">
-        <v>182</v>
+        <v>111</v>
       </c>
       <c r="B112" s="16">
         <v>31863</v>
@@ -12169,9 +12243,9 @@
         <v>0.26804491282916293</v>
       </c>
     </row>
-    <row r="113" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="23">
-        <v>183</v>
+        <v>112</v>
       </c>
       <c r="B113" s="13">
         <v>31864</v>
@@ -12264,9 +12338,9 @@
         <v>0.31063274402276525</v>
       </c>
     </row>
-    <row r="114" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="23">
-        <v>184</v>
+        <v>113</v>
       </c>
       <c r="B114" s="16">
         <v>31862</v>
@@ -12359,9 +12433,9 @@
         <v>1.1605885848184239</v>
       </c>
     </row>
-    <row r="115" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="23">
-        <v>185</v>
+        <v>114</v>
       </c>
       <c r="B115" s="13">
         <v>31870</v>
@@ -12454,9 +12528,9 @@
         <v>4.5104792945354528E-2</v>
       </c>
     </row>
-    <row r="116" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="23">
-        <v>186</v>
+        <v>115</v>
       </c>
       <c r="B116" s="16">
         <v>31871</v>
@@ -12549,9 +12623,9 @@
         <v>0.24453748618863985</v>
       </c>
     </row>
-    <row r="117" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="23">
-        <v>188</v>
+        <v>116</v>
       </c>
       <c r="B117" s="16">
         <v>31865</v>
@@ -12644,9 +12718,9 @@
         <v>0.67906967540065355</v>
       </c>
     </row>
-    <row r="118" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="23">
-        <v>189</v>
+        <v>117</v>
       </c>
       <c r="B118" s="13">
         <v>31873</v>
@@ -12739,9 +12813,9 @@
         <v>0.73742156011434479</v>
       </c>
     </row>
-    <row r="119" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="23">
-        <v>190</v>
+        <v>118</v>
       </c>
       <c r="B119" s="16">
         <v>31878</v>
@@ -12832,9 +12906,9 @@
       </c>
       <c r="AE119" s="17"/>
     </row>
-    <row r="120" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="23">
-        <v>193</v>
+        <v>119</v>
       </c>
       <c r="B120" s="13">
         <v>31890</v>
@@ -12927,9 +13001,9 @@
         <v>0.32108670309600001</v>
       </c>
     </row>
-    <row r="121" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="23">
-        <v>195</v>
+        <v>120</v>
       </c>
       <c r="B121" s="13">
         <v>31895</v>
@@ -13024,7 +13098,7 @@
     </row>
     <row r="122" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="23">
-        <v>196</v>
+        <v>121</v>
       </c>
       <c r="B122" s="16">
         <v>31899</v>
@@ -13117,9 +13191,9 @@
         <v>0.93626914317738263</v>
       </c>
     </row>
-    <row r="123" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="23">
-        <v>198</v>
+        <v>122</v>
       </c>
       <c r="B123" s="16">
         <v>31906</v>
@@ -13212,9 +13286,9 @@
         <v>0.27386711731062435</v>
       </c>
     </row>
-    <row r="124" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="23">
-        <v>200</v>
+        <v>123</v>
       </c>
       <c r="B124" s="16">
         <v>31914</v>
@@ -13307,9 +13381,9 @@
         <v>0.37601425701227598</v>
       </c>
     </row>
-    <row r="125" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="23">
-        <v>201</v>
+        <v>124</v>
       </c>
       <c r="B125" s="13">
         <v>31917</v>
@@ -13402,9 +13476,9 @@
         <v>5.4906726096179123E-2</v>
       </c>
     </row>
-    <row r="126" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="23">
-        <v>203</v>
+        <v>125</v>
       </c>
       <c r="B126" s="13">
         <v>31924</v>
@@ -13497,9 +13571,9 @@
         <v>1.4914097682939695</v>
       </c>
     </row>
-    <row r="127" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="23">
-        <v>204</v>
+        <v>126</v>
       </c>
       <c r="B127" s="16">
         <v>31939</v>
@@ -13594,7 +13668,7 @@
     </row>
     <row r="128" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="23">
-        <v>205</v>
+        <v>127</v>
       </c>
       <c r="B128" s="13">
         <v>31927</v>
@@ -13687,9 +13761,9 @@
         <v>0.90742152564912293</v>
       </c>
     </row>
-    <row r="129" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="23">
-        <v>206</v>
+        <v>128</v>
       </c>
       <c r="B129" s="16">
         <v>31935</v>
@@ -13782,9 +13856,9 @@
         <v>1.9638664161330051</v>
       </c>
     </row>
-    <row r="130" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="23">
-        <v>207</v>
+        <v>129</v>
       </c>
       <c r="B130" s="13">
         <v>31931</v>
@@ -13877,9 +13951,9 @@
         <v>7.5670900061900345E-2</v>
       </c>
     </row>
-    <row r="131" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="23">
-        <v>208</v>
+        <v>130</v>
       </c>
       <c r="B131" s="16">
         <v>31933</v>
@@ -13972,9 +14046,9 @@
         <v>0.47909013937829797</v>
       </c>
     </row>
-    <row r="132" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="23">
-        <v>209</v>
+        <v>131</v>
       </c>
       <c r="B132" s="13">
         <v>31932</v>
@@ -14067,9 +14141,9 @@
         <v>0.11378458873050915</v>
       </c>
     </row>
-    <row r="133" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="23">
-        <v>210</v>
+        <v>132</v>
       </c>
       <c r="B133" s="16">
         <v>31926</v>
@@ -14162,7 +14236,7 @@
     </row>
     <row r="134" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="23">
-        <v>211</v>
+        <v>133</v>
       </c>
       <c r="B134" s="13">
         <v>31948</v>
@@ -14255,9 +14329,9 @@
         <v>0.77431489108380402</v>
       </c>
     </row>
-    <row r="135" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="23">
-        <v>212</v>
+        <v>134</v>
       </c>
       <c r="B135" s="16">
         <v>31951</v>
@@ -14350,9 +14424,9 @@
         <v>0.74038871172046472</v>
       </c>
     </row>
-    <row r="136" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="23">
-        <v>213</v>
+        <v>135</v>
       </c>
       <c r="B136" s="13">
         <v>31945</v>
@@ -14447,7 +14521,7 @@
     </row>
     <row r="137" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="23">
-        <v>214</v>
+        <v>136</v>
       </c>
       <c r="B137" s="16">
         <v>31949</v>
@@ -14542,7 +14616,7 @@
     </row>
     <row r="138" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="23">
-        <v>215</v>
+        <v>137</v>
       </c>
       <c r="B138" s="13">
         <v>31953</v>
@@ -14635,9 +14709,9 @@
         <v>0.7877180071497133</v>
       </c>
     </row>
-    <row r="139" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="23">
-        <v>216</v>
+        <v>138</v>
       </c>
       <c r="B139" s="16">
         <v>31943</v>
@@ -14730,9 +14804,9 @@
         <v>7.2614704034925384E-2</v>
       </c>
     </row>
-    <row r="140" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="23">
-        <v>221</v>
+        <v>139</v>
       </c>
       <c r="B140" s="13">
         <v>31955</v>
@@ -14825,9 +14899,9 @@
         <v>5.8484485764134092E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="23">
-        <v>222</v>
+        <v>140</v>
       </c>
       <c r="B141" s="16">
         <v>31968</v>
@@ -14920,9 +14994,9 @@
         <v>0.58667165822938927</v>
       </c>
     </row>
-    <row r="142" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="23">
-        <v>223</v>
+        <v>141</v>
       </c>
       <c r="B142" s="13">
         <v>31972</v>
@@ -15015,9 +15089,9 @@
         <v>6.6783592659155067E-2</v>
       </c>
     </row>
-    <row r="143" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="23">
-        <v>225</v>
+        <v>142</v>
       </c>
       <c r="B143" s="13">
         <v>31992</v>
@@ -15110,9 +15184,9 @@
         <v>1.3043700899097965</v>
       </c>
     </row>
-    <row r="144" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="23">
-        <v>230</v>
+        <v>143</v>
       </c>
       <c r="B144" s="16">
         <v>31988</v>
@@ -15205,9 +15279,9 @@
         <v>4.967543211734763E-2</v>
       </c>
     </row>
-    <row r="145" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="23">
-        <v>234</v>
+        <v>144</v>
       </c>
       <c r="B145" s="16">
         <v>32007</v>
@@ -15300,9 +15374,9 @@
         <v>0.12730557001373463</v>
       </c>
     </row>
-    <row r="146" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="23">
-        <v>235</v>
+        <v>145</v>
       </c>
       <c r="B146" s="13">
         <v>32012</v>
@@ -15395,9 +15469,9 @@
         <v>3.2139029334305964</v>
       </c>
     </row>
-    <row r="147" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="23">
-        <v>236</v>
+        <v>146</v>
       </c>
       <c r="B147" s="16">
         <v>32013</v>
@@ -15490,9 +15564,9 @@
         <v>0.72312005743172081</v>
       </c>
     </row>
-    <row r="148" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="23">
-        <v>237</v>
+        <v>147</v>
       </c>
       <c r="B148" s="13">
         <v>32014</v>
@@ -15585,9 +15659,9 @@
         <v>9.1270516793306514E-2</v>
       </c>
     </row>
-    <row r="149" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="23">
-        <v>238</v>
+        <v>148</v>
       </c>
       <c r="B149" s="16">
         <v>32015</v>
@@ -15680,9 +15754,9 @@
         <v>1.0584579587607248</v>
       </c>
     </row>
-    <row r="150" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="23">
-        <v>239</v>
+        <v>149</v>
       </c>
       <c r="B150" s="13">
         <v>32032</v>
@@ -15775,9 +15849,9 @@
         <v>0.38357884108130391</v>
       </c>
     </row>
-    <row r="151" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="23">
-        <v>242</v>
+        <v>150</v>
       </c>
       <c r="B151" s="16">
         <v>32033</v>
@@ -15870,9 +15944,9 @@
         <v>3.3336878659715394E-2</v>
       </c>
     </row>
-    <row r="152" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="23">
-        <v>243</v>
+        <v>151</v>
       </c>
       <c r="B152" s="13">
         <v>32048</v>
@@ -15965,9 +16039,9 @@
         <v>6.5584742953255143E-2</v>
       </c>
     </row>
-    <row r="153" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="23">
-        <v>244</v>
+        <v>152</v>
       </c>
       <c r="B153" s="16">
         <v>32047</v>
@@ -16060,9 +16134,9 @@
         <v>0.11146372277184344</v>
       </c>
     </row>
-    <row r="154" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="23">
-        <v>245</v>
+        <v>153</v>
       </c>
       <c r="B154" s="13">
         <v>32057</v>
@@ -16155,9 +16229,9 @@
         <v>3.5107544920202717E-2</v>
       </c>
     </row>
-    <row r="155" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="23">
-        <v>246</v>
+        <v>154</v>
       </c>
       <c r="B155" s="16">
         <v>32051</v>
@@ -16251,9 +16325,9 @@
         <v>1.7726080803401676</v>
       </c>
     </row>
-    <row r="156" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="23">
-        <v>247</v>
+        <v>155</v>
       </c>
       <c r="B156" s="13">
         <v>32063</v>
@@ -16346,9 +16420,9 @@
         <v>0.67558283308064249</v>
       </c>
     </row>
-    <row r="157" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="23">
-        <v>249</v>
+        <v>156</v>
       </c>
       <c r="B157" s="13">
         <v>32074</v>
@@ -16441,9 +16515,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="23">
-        <v>252</v>
+        <v>157</v>
       </c>
       <c r="B158" s="16">
         <v>32071</v>
@@ -16536,9 +16610,9 @@
         <v>0.35293716927272728</v>
       </c>
     </row>
-    <row r="159" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="23">
-        <v>253</v>
+        <v>158</v>
       </c>
       <c r="B159" s="13">
         <v>32081</v>
@@ -16631,9 +16705,9 @@
         <v>6.0959529495959577E-2</v>
       </c>
     </row>
-    <row r="160" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="23">
-        <v>254</v>
+        <v>159</v>
       </c>
       <c r="B160" s="16">
         <v>32086</v>
@@ -16726,9 +16800,9 @@
         <v>0.25794775843903023</v>
       </c>
     </row>
-    <row r="161" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="23">
-        <v>257</v>
+        <v>160</v>
       </c>
       <c r="B161" s="13">
         <v>32089</v>
@@ -16821,9 +16895,9 @@
         <v>0.31898600352229323</v>
       </c>
     </row>
-    <row r="162" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="23">
-        <v>258</v>
+        <v>161</v>
       </c>
       <c r="B162" s="16">
         <v>32104</v>
@@ -16916,9 +16990,9 @@
         <v>0.34514714626589182</v>
       </c>
     </row>
-    <row r="163" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="23">
-        <v>259</v>
+        <v>162</v>
       </c>
       <c r="B163" s="13">
         <v>32105</v>
@@ -17011,9 +17085,9 @@
         <v>0.31545712829436828</v>
       </c>
     </row>
-    <row r="164" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="23">
-        <v>262</v>
+        <v>163</v>
       </c>
       <c r="B164" s="16">
         <v>32127</v>
@@ -17106,9 +17180,9 @@
         <v>0.63233786644680068</v>
       </c>
     </row>
-    <row r="165" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="23">
-        <v>263</v>
+        <v>164</v>
       </c>
       <c r="B165" s="13">
         <v>32129</v>
@@ -17201,9 +17275,9 @@
         <v>1.442026644395441</v>
       </c>
     </row>
-    <row r="166" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="23">
-        <v>264</v>
+        <v>165</v>
       </c>
       <c r="B166" s="16">
         <v>32130</v>
@@ -17296,9 +17370,9 @@
         <v>0.33342873875715351</v>
       </c>
     </row>
-    <row r="167" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="23">
-        <v>265</v>
+        <v>166</v>
       </c>
       <c r="B167" s="13">
         <v>32134</v>
@@ -17391,9 +17465,9 @@
         <v>0.68620006004005563</v>
       </c>
     </row>
-    <row r="168" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="23">
-        <v>266</v>
+        <v>167</v>
       </c>
       <c r="B168" s="16">
         <v>32138</v>
@@ -17486,9 +17560,9 @@
         <v>0.13611759074754531</v>
       </c>
     </row>
-    <row r="169" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="23">
-        <v>267</v>
+        <v>168</v>
       </c>
       <c r="B169" s="13">
         <v>32133</v>
@@ -17581,9 +17655,9 @@
         <v>0.12750802235484152</v>
       </c>
     </row>
-    <row r="170" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="23">
-        <v>269</v>
+        <v>169</v>
       </c>
       <c r="B170" s="13">
         <v>32162</v>
@@ -17676,9 +17750,9 @@
         <v>3.6617603696221267E-2</v>
       </c>
     </row>
-    <row r="171" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="23">
-        <v>271</v>
+        <v>170</v>
       </c>
       <c r="B171" s="13">
         <v>32166</v>
@@ -17771,9 +17845,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="23">
-        <v>273</v>
+        <v>171</v>
       </c>
       <c r="B172" s="13">
         <v>32191</v>
@@ -17866,9 +17940,9 @@
         <v>0.25903609556116164</v>
       </c>
     </row>
-    <row r="173" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="23">
-        <v>274</v>
+        <v>172</v>
       </c>
       <c r="B173" s="16">
         <v>32193</v>
@@ -17961,9 +18035,9 @@
         <v>0.57143368857807042</v>
       </c>
     </row>
-    <row r="174" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="23">
-        <v>276</v>
+        <v>173</v>
       </c>
       <c r="B174" s="16">
         <v>32197</v>
@@ -18058,7 +18132,7 @@
     </row>
     <row r="175" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="23">
-        <v>277</v>
+        <v>174</v>
       </c>
       <c r="B175" s="13">
         <v>32195</v>
@@ -18151,9 +18225,9 @@
         <v>0.87087258488641639</v>
       </c>
     </row>
-    <row r="176" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="23">
-        <v>279</v>
+        <v>175</v>
       </c>
       <c r="B176" s="13">
         <v>32253</v>
@@ -18246,9 +18320,9 @@
         <v>1.2124982736146275</v>
       </c>
     </row>
-    <row r="177" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="23">
-        <v>280</v>
+        <v>176</v>
       </c>
       <c r="B177" s="16">
         <v>32254</v>
@@ -18341,9 +18415,9 @@
         <v>0.1946890015421559</v>
       </c>
     </row>
-    <row r="178" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="23">
-        <v>281</v>
+        <v>177</v>
       </c>
       <c r="B178" s="13">
         <v>32257</v>
@@ -18436,9 +18510,9 @@
         <v>0.38872031289264486</v>
       </c>
     </row>
-    <row r="179" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="23">
-        <v>282</v>
+        <v>178</v>
       </c>
       <c r="B179" s="16">
         <v>32250</v>
@@ -18531,9 +18605,9 @@
         <v>1.4563079439323108</v>
       </c>
     </row>
-    <row r="180" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="23">
-        <v>283</v>
+        <v>179</v>
       </c>
       <c r="B180" s="13">
         <v>32245</v>
@@ -18626,9 +18700,9 @@
         <v>0.29831887674972646</v>
       </c>
     </row>
-    <row r="181" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="23">
-        <v>285</v>
+        <v>180</v>
       </c>
       <c r="B181" s="13">
         <v>32252</v>
@@ -18721,9 +18795,9 @@
         <v>1.6121001331251392</v>
       </c>
     </row>
-    <row r="182" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="23">
-        <v>287</v>
+        <v>181</v>
       </c>
       <c r="B182" s="13">
         <v>32258</v>
@@ -18816,9 +18890,9 @@
         <v>0.25450318003128986</v>
       </c>
     </row>
-    <row r="183" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="23">
-        <v>292</v>
+        <v>182</v>
       </c>
       <c r="B183" s="16">
         <v>32278</v>
@@ -18909,9 +18983,9 @@
       </c>
       <c r="AE183" s="17"/>
     </row>
-    <row r="184" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="23">
-        <v>295</v>
+        <v>183</v>
       </c>
       <c r="B184" s="13">
         <v>32285</v>
@@ -19004,9 +19078,9 @@
         <v>3.8725488406944744E-2</v>
       </c>
     </row>
-    <row r="185" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="23">
-        <v>296</v>
+        <v>184</v>
       </c>
       <c r="B185" s="16">
         <v>32288</v>
@@ -19099,9 +19173,9 @@
         <v>8.0535776895652181E-2</v>
       </c>
     </row>
-    <row r="186" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="23">
-        <v>297</v>
+        <v>185</v>
       </c>
       <c r="B186" s="13">
         <v>32289</v>
@@ -19194,9 +19268,9 @@
         <v>0.12184788482527879</v>
       </c>
     </row>
-    <row r="187" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="23">
-        <v>298</v>
+        <v>186</v>
       </c>
       <c r="B187" s="16">
         <v>32292</v>
@@ -19289,9 +19363,9 @@
         <v>0.42090088571423151</v>
       </c>
     </row>
-    <row r="188" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="23">
-        <v>300</v>
+        <v>187</v>
       </c>
       <c r="B188" s="16">
         <v>32296</v>
@@ -19384,9 +19458,9 @@
         <v>4.0272957878145457E-2</v>
       </c>
     </row>
-    <row r="189" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="23">
-        <v>301</v>
+        <v>188</v>
       </c>
       <c r="B189" s="13">
         <v>32298</v>
@@ -19479,9 +19553,9 @@
         <v>7.2232066660011876E-2</v>
       </c>
     </row>
-    <row r="190" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="23">
-        <v>303</v>
+        <v>189</v>
       </c>
       <c r="B190" s="13">
         <v>32297</v>
@@ -19574,9 +19648,9 @@
         <v>3.6681366480972068E-2</v>
       </c>
     </row>
-    <row r="191" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="23">
-        <v>304</v>
+        <v>190</v>
       </c>
       <c r="B191" s="16">
         <v>32323</v>
@@ -19669,9 +19743,9 @@
         <v>4.8286178248228763E-2</v>
       </c>
     </row>
-    <row r="192" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="23">
-        <v>306</v>
+        <v>191</v>
       </c>
       <c r="B192" s="16">
         <v>32327</v>
@@ -19764,9 +19838,9 @@
         <v>3.6864877543286337E-2</v>
       </c>
     </row>
-    <row r="193" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="23">
-        <v>307</v>
+        <v>192</v>
       </c>
       <c r="B193" s="13">
         <v>32333</v>
@@ -19859,9 +19933,9 @@
         <v>2.5542401910578116E-2</v>
       </c>
     </row>
-    <row r="194" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="23">
-        <v>309</v>
+        <v>193</v>
       </c>
       <c r="B194" s="13">
         <v>32337</v>
@@ -19954,9 +20028,9 @@
         <v>0.53151142331963475</v>
       </c>
     </row>
-    <row r="195" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="23">
-        <v>310</v>
+        <v>194</v>
       </c>
       <c r="B195" s="16">
         <v>32350</v>
@@ -20049,9 +20123,9 @@
         <v>3.2385661241970475E-2</v>
       </c>
     </row>
-    <row r="196" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="23">
-        <v>311</v>
+        <v>195</v>
       </c>
       <c r="B196" s="13">
         <v>32357</v>
@@ -20144,9 +20218,9 @@
         <v>0.32578226666166898</v>
       </c>
     </row>
-    <row r="197" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="23">
-        <v>312</v>
+        <v>196</v>
       </c>
       <c r="B197" s="16">
         <v>32355</v>
@@ -20237,9 +20311,9 @@
       </c>
       <c r="AE197" s="17"/>
     </row>
-    <row r="198" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="23">
-        <v>313</v>
+        <v>197</v>
       </c>
       <c r="B198" s="13">
         <v>32356</v>
@@ -20334,7 +20408,7 @@
     </row>
     <row r="199" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="23">
-        <v>315</v>
+        <v>198</v>
       </c>
       <c r="B199" s="13">
         <v>32370</v>
@@ -20427,9 +20501,9 @@
         <v>0.80753025802194411</v>
       </c>
     </row>
-    <row r="200" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="23">
-        <v>316</v>
+        <v>199</v>
       </c>
       <c r="B200" s="16">
         <v>32371</v>
@@ -20522,9 +20596,9 @@
         <v>5.0563339354955605E-2</v>
       </c>
     </row>
-    <row r="201" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="23">
-        <v>318</v>
+        <v>200</v>
       </c>
       <c r="B201" s="16">
         <v>32380</v>
@@ -20617,9 +20691,9 @@
         <v>0.10599550733914423</v>
       </c>
     </row>
-    <row r="202" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="23">
-        <v>320</v>
+        <v>201</v>
       </c>
       <c r="B202" s="16">
         <v>32399</v>
@@ -20712,9 +20786,9 @@
         <v>0.13497601065263146</v>
       </c>
     </row>
-    <row r="203" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="23">
-        <v>321</v>
+        <v>202</v>
       </c>
       <c r="B203" s="13">
         <v>32403</v>
@@ -20807,9 +20881,9 @@
         <v>2.4856561020012151E-2</v>
       </c>
     </row>
-    <row r="204" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="23">
-        <v>322</v>
+        <v>203</v>
       </c>
       <c r="B204" s="16">
         <v>32405</v>
@@ -20902,9 +20976,9 @@
         <v>0.5145713543694953</v>
       </c>
     </row>
-    <row r="205" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="23">
-        <v>327</v>
+        <v>204</v>
       </c>
       <c r="B205" s="13">
         <v>32442</v>
@@ -20997,9 +21071,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="23">
-        <v>329</v>
+        <v>205</v>
       </c>
       <c r="B206" s="13">
         <v>32436</v>
@@ -21092,9 +21166,9 @@
         <v>0.24273460390610674</v>
       </c>
     </row>
-    <row r="207" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="23">
-        <v>332</v>
+        <v>206</v>
       </c>
       <c r="B207" s="16">
         <v>32475</v>
@@ -21187,9 +21261,9 @@
         <v>1.0002156302819833</v>
       </c>
     </row>
-    <row r="208" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="23">
-        <v>336</v>
+        <v>207</v>
       </c>
       <c r="B208" s="16">
         <v>32486</v>
@@ -21282,9 +21356,9 @@
         <v>2.3612232690146288E-2</v>
       </c>
     </row>
-    <row r="209" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="23">
-        <v>337</v>
+        <v>208</v>
       </c>
       <c r="B209" s="13">
         <v>32510</v>
@@ -21377,9 +21451,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="23">
-        <v>338</v>
+        <v>209</v>
       </c>
       <c r="B210" s="16">
         <v>32503</v>
@@ -21473,9 +21547,9 @@
         <v>3.7336623510238587E-2</v>
       </c>
     </row>
-    <row r="211" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="23">
-        <v>339</v>
+        <v>210</v>
       </c>
       <c r="B211" s="13">
         <v>32506</v>
@@ -21568,9 +21642,9 @@
         <v>9.7679506854981918E-2</v>
       </c>
     </row>
-    <row r="212" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="23">
-        <v>342</v>
+        <v>211</v>
       </c>
       <c r="B212" s="16">
         <v>32525</v>
@@ -21665,7 +21739,7 @@
     </row>
     <row r="213" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="23">
-        <v>344</v>
+        <v>212</v>
       </c>
       <c r="B213" s="16">
         <v>32535</v>
@@ -21758,9 +21832,9 @@
         <v>0.77535019249684334</v>
       </c>
     </row>
-    <row r="214" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="23">
-        <v>346</v>
+        <v>213</v>
       </c>
       <c r="B214" s="16">
         <v>32554</v>
@@ -21854,9 +21928,9 @@
         <v>0.93354865743082172</v>
       </c>
     </row>
-    <row r="215" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="23">
-        <v>347</v>
+        <v>214</v>
       </c>
       <c r="B215" s="13">
         <v>32553</v>
@@ -21949,9 +22023,9 @@
         <v>6.7214291976851928E-2</v>
       </c>
     </row>
-    <row r="216" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="23">
-        <v>349</v>
+        <v>215</v>
       </c>
       <c r="B216" s="13">
         <v>32563</v>
@@ -22044,9 +22118,9 @@
         <v>0.26246864308047269</v>
       </c>
     </row>
-    <row r="217" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="23">
-        <v>350</v>
+        <v>216</v>
       </c>
       <c r="B217" s="16">
         <v>32561</v>
@@ -22139,9 +22213,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="23">
-        <v>352</v>
+        <v>217</v>
       </c>
       <c r="B218" s="16">
         <v>32573</v>
@@ -22234,9 +22308,9 @@
         <v>4.1133972476275676E-2</v>
       </c>
     </row>
-    <row r="219" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="23">
-        <v>353</v>
+        <v>218</v>
       </c>
       <c r="B219" s="13">
         <v>32580</v>
@@ -22327,9 +22401,9 @@
       </c>
       <c r="AE219" s="17"/>
     </row>
-    <row r="220" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="23">
-        <v>354</v>
+        <v>219</v>
       </c>
       <c r="B220" s="16">
         <v>32586</v>
@@ -22422,9 +22496,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="23">
-        <v>355</v>
+        <v>220</v>
       </c>
       <c r="B221" s="13">
         <v>32572</v>
@@ -22517,9 +22591,9 @@
         <v>9.6713500466666671E-2</v>
       </c>
     </row>
-    <row r="222" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="23">
-        <v>358</v>
+        <v>221</v>
       </c>
       <c r="B222" s="16">
         <v>32597</v>
@@ -22612,9 +22686,9 @@
         <v>9.3226032398125408E-2</v>
       </c>
     </row>
-    <row r="223" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="23">
-        <v>361</v>
+        <v>222</v>
       </c>
       <c r="B223" s="13">
         <v>32605</v>
@@ -22707,9 +22781,9 @@
         <v>2.8057954254330716E-2</v>
       </c>
     </row>
-    <row r="224" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="23">
-        <v>363</v>
+        <v>223</v>
       </c>
       <c r="B224" s="13">
         <v>32603</v>
@@ -22804,7 +22878,7 @@
     </row>
     <row r="225" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="23">
-        <v>365</v>
+        <v>224</v>
       </c>
       <c r="B225" s="13">
         <v>32611</v>
@@ -22897,9 +22971,9 @@
         <v>0.89747044707912538</v>
       </c>
     </row>
-    <row r="226" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="23">
-        <v>368</v>
+        <v>225</v>
       </c>
       <c r="B226" s="16">
         <v>32623</v>
@@ -22992,9 +23066,9 @@
         <v>0.10037376700857506</v>
       </c>
     </row>
-    <row r="227" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="23">
-        <v>369</v>
+        <v>226</v>
       </c>
       <c r="B227" s="13">
         <v>32622</v>
@@ -23087,9 +23161,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="23">
-        <v>376</v>
+        <v>227</v>
       </c>
       <c r="B228" s="16">
         <v>32655</v>
@@ -23182,9 +23256,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="23">
-        <v>378</v>
+        <v>228</v>
       </c>
       <c r="B229" s="16">
         <v>32672</v>
@@ -23277,9 +23351,9 @@
         <v>1.7588739811205951</v>
       </c>
     </row>
-    <row r="230" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="23">
-        <v>379</v>
+        <v>229</v>
       </c>
       <c r="B230" s="13">
         <v>32692</v>
@@ -23372,9 +23446,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="23">
-        <v>380</v>
+        <v>230</v>
       </c>
       <c r="B231" s="16">
         <v>32693</v>
@@ -23467,9 +23541,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="23">
-        <v>383</v>
+        <v>231</v>
       </c>
       <c r="B232" s="13">
         <v>32698</v>
@@ -23562,9 +23636,9 @@
         <v>3.3543153948069858E-2</v>
       </c>
     </row>
-    <row r="233" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="23">
-        <v>385</v>
+        <v>232</v>
       </c>
       <c r="B233" s="13">
         <v>32704</v>
@@ -23657,9 +23731,9 @@
         <v>2.5030581189388085E-2</v>
       </c>
     </row>
-    <row r="234" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="23">
-        <v>386</v>
+        <v>233</v>
       </c>
       <c r="B234" s="16">
         <v>32717</v>
@@ -23752,9 +23826,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="23">
-        <v>387</v>
+        <v>234</v>
       </c>
       <c r="B235" s="13">
         <v>32726</v>
@@ -23847,9 +23921,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="23">
-        <v>390</v>
+        <v>235</v>
       </c>
       <c r="B236" s="16">
         <v>32740</v>
@@ -23942,9 +24016,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="23">
-        <v>391</v>
+        <v>236</v>
       </c>
       <c r="B237" s="13">
         <v>32743</v>
@@ -24037,15 +24111,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="23">
-        <v>392</v>
+        <v>237</v>
       </c>
       <c r="B238" s="16">
         <v>32737</v>
       </c>
-      <c r="C238" s="16" t="s">
-        <v>274</v>
+      <c r="C238" s="28">
+        <v>25560</v>
       </c>
       <c r="D238" s="15" t="s">
         <v>267</v>
@@ -24132,9 +24206,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="23">
-        <v>395</v>
+        <v>238</v>
       </c>
       <c r="B239" s="13">
         <v>32746</v>
@@ -24227,9 +24301,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:31" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:31" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="23">
-        <v>399</v>
+        <v>239</v>
       </c>
       <c r="B240" s="13">
         <v>32759</v>
@@ -24322,9 +24396,9 @@
         <v>1.381967797982359</v>
       </c>
     </row>
-    <row r="241" spans="1:32" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:32" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="23">
-        <v>400</v>
+        <v>240</v>
       </c>
       <c r="B241" s="16">
         <v>32758</v>
@@ -24417,9 +24491,9 @@
         <v>0.18181321084864394</v>
       </c>
     </row>
-    <row r="242" spans="1:32" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:32" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="23">
-        <v>402</v>
+        <v>241</v>
       </c>
       <c r="B242" s="16">
         <v>32777</v>
@@ -24512,15 +24586,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:32" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:32" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="23">
-        <v>405</v>
+        <v>242</v>
       </c>
       <c r="B243" s="13">
         <v>32809</v>
       </c>
-      <c r="C243" s="13" t="s">
-        <v>275</v>
+      <c r="C243" s="29">
+        <v>25730</v>
       </c>
       <c r="D243" s="12" t="s">
         <v>272</v>
@@ -24607,9 +24681,9 @@
         <v>1.222857234058836E-2</v>
       </c>
     </row>
-    <row r="244" spans="1:32" ht="11.85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:32" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="23">
-        <v>409</v>
+        <v>243</v>
       </c>
       <c r="B244" s="13">
         <v>32815</v>
@@ -24703,14 +24777,1531 @@
       </c>
     </row>
     <row r="245" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A245" s="23">
+        <v>244</v>
+      </c>
+      <c r="B245" s="13">
+        <v>28689</v>
+      </c>
+      <c r="C245" s="13">
+        <v>24754</v>
+      </c>
+      <c r="D245" s="26" t="s">
+        <v>274</v>
+      </c>
+      <c r="E245" s="9">
+        <v>64780000</v>
+      </c>
+      <c r="F245" s="9">
+        <v>3625016</v>
+      </c>
+      <c r="G245" s="9">
+        <v>0</v>
+      </c>
+      <c r="H245" s="9">
+        <v>0</v>
+      </c>
+      <c r="I245" s="9">
+        <v>13000000</v>
+      </c>
+      <c r="J245" s="10">
+        <v>2175000</v>
+      </c>
+      <c r="K245" s="9">
+        <v>0</v>
+      </c>
+      <c r="L245" s="9">
+        <v>1087500</v>
+      </c>
+      <c r="M245" s="9">
+        <v>1087000</v>
+      </c>
+      <c r="N245" s="9">
+        <v>1800000</v>
+      </c>
+      <c r="O245" s="9">
+        <v>0</v>
+      </c>
+      <c r="P245" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q245" s="9">
+        <v>87554516</v>
+      </c>
+      <c r="R245" s="8">
+        <v>41032732</v>
+      </c>
+      <c r="S245" s="8">
+        <v>1634500</v>
+      </c>
+      <c r="T245" s="8">
+        <v>0</v>
+      </c>
+      <c r="U245" s="8">
+        <v>0</v>
+      </c>
+      <c r="V245" s="8">
+        <v>16900790</v>
+      </c>
+      <c r="W245" s="8">
+        <v>10800306</v>
+      </c>
+      <c r="X245" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y245" s="8">
+        <v>961040</v>
+      </c>
+      <c r="Z245" s="8">
+        <v>2440528.79739</v>
+      </c>
+      <c r="AA245" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB245" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC245" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD245" s="11">
+        <v>73769896.797389999</v>
+      </c>
+      <c r="AE245" s="18">
+        <v>0.86</v>
+      </c>
       <c r="AF245" s="24"/>
     </row>
+    <row r="246" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A246" s="23">
+        <v>245</v>
+      </c>
+      <c r="B246" s="16">
+        <v>29585</v>
+      </c>
+      <c r="C246" s="16">
+        <v>24776</v>
+      </c>
+      <c r="D246" s="27" t="s">
+        <v>275</v>
+      </c>
+      <c r="E246" s="9">
+        <v>0</v>
+      </c>
+      <c r="F246" s="9">
+        <v>2995380</v>
+      </c>
+      <c r="G246" s="9">
+        <v>4474580</v>
+      </c>
+      <c r="H246" s="9">
+        <v>0</v>
+      </c>
+      <c r="I246" s="9">
+        <v>66564000</v>
+      </c>
+      <c r="J246" s="10">
+        <v>5916800</v>
+      </c>
+      <c r="K246" s="9">
+        <v>0</v>
+      </c>
+      <c r="L246" s="9">
+        <v>2958400</v>
+      </c>
+      <c r="M246" s="9">
+        <v>0</v>
+      </c>
+      <c r="N246" s="9">
+        <v>17750400</v>
+      </c>
+      <c r="O246" s="9">
+        <v>0</v>
+      </c>
+      <c r="P246" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q246" s="9">
+        <v>100659560</v>
+      </c>
+      <c r="R246" s="8">
+        <v>0</v>
+      </c>
+      <c r="S246" s="8">
+        <v>1295500</v>
+      </c>
+      <c r="T246" s="8">
+        <v>0</v>
+      </c>
+      <c r="U246" s="8">
+        <v>0</v>
+      </c>
+      <c r="V246" s="8">
+        <v>51605380</v>
+      </c>
+      <c r="W246" s="8">
+        <v>3775676</v>
+      </c>
+      <c r="X246" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y246" s="8">
+        <v>1279466</v>
+      </c>
+      <c r="Z246" s="8">
+        <v>3487057.5402299999</v>
+      </c>
+      <c r="AA246" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB246" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC246" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD246" s="11">
+        <v>61443079.540229999</v>
+      </c>
+      <c r="AE246" s="14">
+        <v>0.74099999999999999</v>
+      </c>
+    </row>
+    <row r="247" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A247" s="23">
+        <v>246</v>
+      </c>
+      <c r="B247" s="13">
+        <v>28567</v>
+      </c>
+      <c r="C247" s="13">
+        <v>24938</v>
+      </c>
+      <c r="D247" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="E247" s="9">
+        <v>59967500</v>
+      </c>
+      <c r="F247" s="9">
+        <v>8291177</v>
+      </c>
+      <c r="G247" s="9">
+        <v>12436766</v>
+      </c>
+      <c r="H247" s="9">
+        <v>0</v>
+      </c>
+      <c r="I247" s="9">
+        <v>55274514</v>
+      </c>
+      <c r="J247" s="10">
+        <v>5526887</v>
+      </c>
+      <c r="K247" s="9">
+        <v>0</v>
+      </c>
+      <c r="L247" s="9">
+        <v>13819122</v>
+      </c>
+      <c r="M247" s="9">
+        <v>100285202</v>
+      </c>
+      <c r="N247" s="9">
+        <v>0</v>
+      </c>
+      <c r="O247" s="9">
+        <v>0</v>
+      </c>
+      <c r="P247" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q247" s="9">
+        <v>255601168</v>
+      </c>
+      <c r="R247" s="8">
+        <v>77223544</v>
+      </c>
+      <c r="S247" s="8">
+        <v>18790499.5</v>
+      </c>
+      <c r="T247" s="8">
+        <v>7911000</v>
+      </c>
+      <c r="U247" s="8">
+        <v>0</v>
+      </c>
+      <c r="V247" s="8">
+        <v>31906255</v>
+      </c>
+      <c r="W247" s="8">
+        <v>13227142</v>
+      </c>
+      <c r="X247" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y247" s="8">
+        <v>7571741.5</v>
+      </c>
+      <c r="Z247" s="8">
+        <v>28290640.810479999</v>
+      </c>
+      <c r="AA247" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB247" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC247" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD247" s="11">
+        <v>184920822.81048</v>
+      </c>
+      <c r="AE247" s="14">
+        <v>0.72299999999999998</v>
+      </c>
+    </row>
+    <row r="248" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A248" s="23">
+        <v>247</v>
+      </c>
+      <c r="B248" s="16">
+        <v>29563</v>
+      </c>
+      <c r="C248" s="16">
+        <v>24942</v>
+      </c>
+      <c r="D248" s="27" t="s">
+        <v>277</v>
+      </c>
+      <c r="E248" s="9">
+        <v>0</v>
+      </c>
+      <c r="F248" s="9">
+        <v>1102908</v>
+      </c>
+      <c r="G248" s="9">
+        <v>0</v>
+      </c>
+      <c r="H248" s="9">
+        <v>0</v>
+      </c>
+      <c r="I248" s="9">
+        <v>7352721</v>
+      </c>
+      <c r="J248" s="10">
+        <v>735272</v>
+      </c>
+      <c r="K248" s="9">
+        <v>0</v>
+      </c>
+      <c r="L248" s="9">
+        <v>1838180</v>
+      </c>
+      <c r="M248" s="9">
+        <v>13436106</v>
+      </c>
+      <c r="N248" s="9">
+        <v>0</v>
+      </c>
+      <c r="O248" s="9">
+        <v>0</v>
+      </c>
+      <c r="P248" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q248" s="9">
+        <v>24465187</v>
+      </c>
+      <c r="R248" s="8">
+        <v>0</v>
+      </c>
+      <c r="S248" s="8">
+        <v>720000</v>
+      </c>
+      <c r="T248" s="8">
+        <v>0</v>
+      </c>
+      <c r="U248" s="8">
+        <v>0</v>
+      </c>
+      <c r="V248" s="8">
+        <v>8763794</v>
+      </c>
+      <c r="W248" s="8">
+        <v>370262.45299999998</v>
+      </c>
+      <c r="X248" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y248" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z248" s="8">
+        <v>3790373.4899200001</v>
+      </c>
+      <c r="AA248" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB248" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC248" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD248" s="11">
+        <v>13644429.942919999</v>
+      </c>
+      <c r="AE248" s="14">
+        <v>0.55800000000000005</v>
+      </c>
+    </row>
+    <row r="249" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A249" s="23">
+        <v>248</v>
+      </c>
+      <c r="B249" s="13">
+        <v>30547</v>
+      </c>
+      <c r="C249" s="13">
+        <v>25008</v>
+      </c>
+      <c r="D249" s="26" t="s">
+        <v>278</v>
+      </c>
+      <c r="E249" s="9">
+        <v>0</v>
+      </c>
+      <c r="F249" s="9">
+        <v>15000000</v>
+      </c>
+      <c r="G249" s="9">
+        <v>20000000</v>
+      </c>
+      <c r="H249" s="9">
+        <v>0</v>
+      </c>
+      <c r="I249" s="9">
+        <v>60000000</v>
+      </c>
+      <c r="J249" s="10">
+        <v>2000000</v>
+      </c>
+      <c r="K249" s="9">
+        <v>0</v>
+      </c>
+      <c r="L249" s="9">
+        <v>10000000</v>
+      </c>
+      <c r="M249" s="9">
+        <v>100000000</v>
+      </c>
+      <c r="N249" s="9">
+        <v>0</v>
+      </c>
+      <c r="O249" s="9">
+        <v>0</v>
+      </c>
+      <c r="P249" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q249" s="9">
+        <v>207000000</v>
+      </c>
+      <c r="R249" s="8">
+        <v>0</v>
+      </c>
+      <c r="S249" s="8">
+        <v>75000</v>
+      </c>
+      <c r="T249" s="8">
+        <v>52389999</v>
+      </c>
+      <c r="U249" s="8">
+        <v>0</v>
+      </c>
+      <c r="V249" s="8">
+        <v>195672121</v>
+      </c>
+      <c r="W249" s="8">
+        <v>1686869.6577300001</v>
+      </c>
+      <c r="X249" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y249" s="8">
+        <v>69365685</v>
+      </c>
+      <c r="Z249" s="8">
+        <v>7457827.7219500002</v>
+      </c>
+      <c r="AA249" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB249" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC249" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD249" s="11">
+        <v>326647502.37967998</v>
+      </c>
+      <c r="AE249" s="25">
+        <v>1.5780000000000001</v>
+      </c>
+    </row>
+    <row r="250" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A250" s="23">
+        <v>249</v>
+      </c>
+      <c r="B250" s="16">
+        <v>30340</v>
+      </c>
+      <c r="C250" s="16">
+        <v>25018</v>
+      </c>
+      <c r="D250" s="27" t="s">
+        <v>279</v>
+      </c>
+      <c r="E250" s="9">
+        <v>184359423</v>
+      </c>
+      <c r="F250" s="9">
+        <v>9549163</v>
+      </c>
+      <c r="G250" s="9">
+        <v>0</v>
+      </c>
+      <c r="H250" s="9">
+        <v>0</v>
+      </c>
+      <c r="I250" s="9">
+        <v>60728511</v>
+      </c>
+      <c r="J250" s="10">
+        <v>7793500</v>
+      </c>
+      <c r="K250" s="9">
+        <v>0</v>
+      </c>
+      <c r="L250" s="9">
+        <v>10610213</v>
+      </c>
+      <c r="M250" s="9">
+        <v>73861125</v>
+      </c>
+      <c r="N250" s="9">
+        <v>0</v>
+      </c>
+      <c r="O250" s="9">
+        <v>0</v>
+      </c>
+      <c r="P250" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q250" s="9">
+        <v>346901935</v>
+      </c>
+      <c r="R250" s="8">
+        <v>141164554.72999999</v>
+      </c>
+      <c r="S250" s="8">
+        <v>17052500</v>
+      </c>
+      <c r="T250" s="8">
+        <v>0</v>
+      </c>
+      <c r="U250" s="8">
+        <v>0</v>
+      </c>
+      <c r="V250" s="8">
+        <v>36654412</v>
+      </c>
+      <c r="W250" s="8">
+        <v>6361032</v>
+      </c>
+      <c r="X250" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y250" s="8">
+        <v>17327489</v>
+      </c>
+      <c r="Z250" s="8">
+        <v>15456230.17522</v>
+      </c>
+      <c r="AA250" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB250" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC250" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD250" s="11">
+        <v>234016217.90522</v>
+      </c>
+      <c r="AE250" s="14">
+        <v>0.67500000000000004</v>
+      </c>
+    </row>
+    <row r="251" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A251" s="23">
+        <v>250</v>
+      </c>
+      <c r="B251" s="13">
+        <v>29995</v>
+      </c>
+      <c r="C251" s="29">
+        <v>25034</v>
+      </c>
+      <c r="D251" s="26" t="s">
+        <v>280</v>
+      </c>
+      <c r="E251" s="9">
+        <v>349947613</v>
+      </c>
+      <c r="F251" s="9">
+        <v>52912500</v>
+      </c>
+      <c r="G251" s="9">
+        <v>0</v>
+      </c>
+      <c r="H251" s="9">
+        <v>0</v>
+      </c>
+      <c r="I251" s="9">
+        <v>141205825</v>
+      </c>
+      <c r="J251" s="10">
+        <v>8818750</v>
+      </c>
+      <c r="K251" s="9">
+        <v>0</v>
+      </c>
+      <c r="L251" s="9">
+        <v>9524250</v>
+      </c>
+      <c r="M251" s="9">
+        <v>110036835</v>
+      </c>
+      <c r="N251" s="9">
+        <v>0</v>
+      </c>
+      <c r="O251" s="9">
+        <v>0</v>
+      </c>
+      <c r="P251" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q251" s="9">
+        <v>672445773</v>
+      </c>
+      <c r="R251" s="8">
+        <v>153323214</v>
+      </c>
+      <c r="S251" s="8">
+        <v>6921817.375</v>
+      </c>
+      <c r="T251" s="8">
+        <v>0</v>
+      </c>
+      <c r="U251" s="8">
+        <v>8144248</v>
+      </c>
+      <c r="V251" s="8">
+        <v>29794801.75</v>
+      </c>
+      <c r="W251" s="8">
+        <v>0</v>
+      </c>
+      <c r="X251" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y251" s="8">
+        <v>13132625.4</v>
+      </c>
+      <c r="Z251" s="8">
+        <v>24005434.12937</v>
+      </c>
+      <c r="AA251" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB251" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC251" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD251" s="11">
+        <v>235322140.65437001</v>
+      </c>
+      <c r="AE251" s="14">
+        <v>0.34994961691040333</v>
+      </c>
+    </row>
+    <row r="252" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A252" s="23">
+        <v>251</v>
+      </c>
+      <c r="B252" s="16">
+        <v>30347</v>
+      </c>
+      <c r="C252" s="16">
+        <v>25072</v>
+      </c>
+      <c r="D252" s="27" t="s">
+        <v>281</v>
+      </c>
+      <c r="E252" s="9">
+        <v>546517088</v>
+      </c>
+      <c r="F252" s="9">
+        <v>14172288</v>
+      </c>
+      <c r="G252" s="9">
+        <v>28344576</v>
+      </c>
+      <c r="H252" s="9">
+        <v>0</v>
+      </c>
+      <c r="I252" s="9">
+        <v>109304832</v>
+      </c>
+      <c r="J252" s="10">
+        <v>5664672</v>
+      </c>
+      <c r="K252" s="9">
+        <v>0</v>
+      </c>
+      <c r="L252" s="9">
+        <v>11336416</v>
+      </c>
+      <c r="M252" s="9">
+        <v>47827936</v>
+      </c>
+      <c r="N252" s="9">
+        <v>0</v>
+      </c>
+      <c r="O252" s="9">
+        <v>0</v>
+      </c>
+      <c r="P252" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q252" s="9">
+        <v>763167808</v>
+      </c>
+      <c r="R252" s="8">
+        <v>484771882.63</v>
+      </c>
+      <c r="S252" s="8">
+        <v>4617046</v>
+      </c>
+      <c r="T252" s="8">
+        <v>45086364</v>
+      </c>
+      <c r="U252" s="8">
+        <v>0</v>
+      </c>
+      <c r="V252" s="8">
+        <v>76548557</v>
+      </c>
+      <c r="W252" s="8">
+        <v>1461684</v>
+      </c>
+      <c r="X252" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y252" s="8">
+        <v>52850744</v>
+      </c>
+      <c r="Z252" s="8">
+        <v>55403530.62878</v>
+      </c>
+      <c r="AA252" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB252" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC252" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD252" s="11">
+        <v>720739808.25878</v>
+      </c>
+      <c r="AE252" s="18">
+        <v>0.94399999999999995</v>
+      </c>
+    </row>
+    <row r="253" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A253" s="23">
+        <v>252</v>
+      </c>
+      <c r="B253" s="13">
+        <v>24568</v>
+      </c>
+      <c r="C253" s="13">
+        <v>25195</v>
+      </c>
+      <c r="D253" s="26" t="s">
+        <v>282</v>
+      </c>
+      <c r="E253" s="9">
+        <v>0</v>
+      </c>
+      <c r="F253" s="9">
+        <v>1909782</v>
+      </c>
+      <c r="G253" s="9">
+        <v>2864673</v>
+      </c>
+      <c r="H253" s="9">
+        <v>0</v>
+      </c>
+      <c r="I253" s="9">
+        <v>69940000</v>
+      </c>
+      <c r="J253" s="10">
+        <v>3392090</v>
+      </c>
+      <c r="K253" s="9">
+        <v>0</v>
+      </c>
+      <c r="L253" s="9">
+        <v>8959664</v>
+      </c>
+      <c r="M253" s="9">
+        <v>82707897</v>
+      </c>
+      <c r="N253" s="9">
+        <v>0</v>
+      </c>
+      <c r="O253" s="9">
+        <v>0</v>
+      </c>
+      <c r="P253" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q253" s="9">
+        <v>169774106</v>
+      </c>
+      <c r="R253" s="8">
+        <v>0</v>
+      </c>
+      <c r="S253" s="8">
+        <v>2733000</v>
+      </c>
+      <c r="T253" s="8">
+        <v>0</v>
+      </c>
+      <c r="U253" s="8">
+        <v>0</v>
+      </c>
+      <c r="V253" s="8">
+        <v>98569876</v>
+      </c>
+      <c r="W253" s="8">
+        <v>9041620</v>
+      </c>
+      <c r="X253" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y253" s="8">
+        <v>26598170</v>
+      </c>
+      <c r="Z253" s="8">
+        <v>19579762.917599998</v>
+      </c>
+      <c r="AA253" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB253" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC253" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD253" s="11">
+        <v>156522428.91760001</v>
+      </c>
+      <c r="AE253" s="18">
+        <v>0.92200000000000004</v>
+      </c>
+    </row>
+    <row r="254" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A254" s="23">
+        <v>253</v>
+      </c>
+      <c r="B254" s="16">
+        <v>31026</v>
+      </c>
+      <c r="C254" s="16">
+        <v>25206</v>
+      </c>
+      <c r="D254" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="E254" s="9">
+        <v>0</v>
+      </c>
+      <c r="F254" s="9">
+        <v>10392052</v>
+      </c>
+      <c r="G254" s="9">
+        <v>16627298</v>
+      </c>
+      <c r="H254" s="9">
+        <v>0</v>
+      </c>
+      <c r="I254" s="9">
+        <v>62352454</v>
+      </c>
+      <c r="J254" s="10">
+        <v>4156807</v>
+      </c>
+      <c r="K254" s="9">
+        <v>0</v>
+      </c>
+      <c r="L254" s="9">
+        <v>2078438</v>
+      </c>
+      <c r="M254" s="9">
+        <v>131271264</v>
+      </c>
+      <c r="N254" s="9">
+        <v>0</v>
+      </c>
+      <c r="O254" s="9">
+        <v>0</v>
+      </c>
+      <c r="P254" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q254" s="9">
+        <v>226878313</v>
+      </c>
+      <c r="R254" s="8">
+        <v>0</v>
+      </c>
+      <c r="S254" s="8">
+        <v>2836500</v>
+      </c>
+      <c r="T254" s="8">
+        <v>0</v>
+      </c>
+      <c r="U254" s="8">
+        <v>0</v>
+      </c>
+      <c r="V254" s="8">
+        <v>113231624</v>
+      </c>
+      <c r="W254" s="8">
+        <v>5983641</v>
+      </c>
+      <c r="X254" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y254" s="8">
+        <v>20578191</v>
+      </c>
+      <c r="Z254" s="8">
+        <v>31948361.939520001</v>
+      </c>
+      <c r="AA254" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB254" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC254" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD254" s="11">
+        <v>174578317.93952</v>
+      </c>
+      <c r="AE254" s="18">
+        <v>0.76900000000000002</v>
+      </c>
+    </row>
+    <row r="255" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A255" s="23">
+        <v>254</v>
+      </c>
+      <c r="B255" s="13">
+        <v>30087</v>
+      </c>
+      <c r="C255" s="13">
+        <v>25234</v>
+      </c>
+      <c r="D255" s="26" t="s">
+        <v>284</v>
+      </c>
+      <c r="E255" s="9">
+        <v>26392491</v>
+      </c>
+      <c r="F255" s="9">
+        <v>2746800</v>
+      </c>
+      <c r="G255" s="9">
+        <v>0</v>
+      </c>
+      <c r="H255" s="9">
+        <v>0</v>
+      </c>
+      <c r="I255" s="9">
+        <v>45665550</v>
+      </c>
+      <c r="J255" s="10">
+        <v>4463550</v>
+      </c>
+      <c r="K255" s="9">
+        <v>0</v>
+      </c>
+      <c r="L255" s="9">
+        <v>1030050</v>
+      </c>
+      <c r="M255" s="9">
+        <v>32989068</v>
+      </c>
+      <c r="N255" s="9">
+        <v>26420783</v>
+      </c>
+      <c r="O255" s="9">
+        <v>0</v>
+      </c>
+      <c r="P255" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q255" s="9">
+        <v>139708292</v>
+      </c>
+      <c r="R255" s="8">
+        <v>30770823.809999999</v>
+      </c>
+      <c r="S255" s="8">
+        <v>662500</v>
+      </c>
+      <c r="T255" s="8">
+        <v>0</v>
+      </c>
+      <c r="U255" s="8">
+        <v>0</v>
+      </c>
+      <c r="V255" s="8">
+        <v>13204902</v>
+      </c>
+      <c r="W255" s="8">
+        <v>2443387</v>
+      </c>
+      <c r="X255" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y255" s="8">
+        <v>2012507.375</v>
+      </c>
+      <c r="Z255" s="8">
+        <v>18023539.816670001</v>
+      </c>
+      <c r="AA255" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB255" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC255" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD255" s="11">
+        <v>67117660.001670003</v>
+      </c>
+      <c r="AE255" s="14">
+        <v>0.59199999999999997</v>
+      </c>
+    </row>
+    <row r="256" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A256" s="23">
+        <v>255</v>
+      </c>
+      <c r="B256" s="16">
+        <v>27079</v>
+      </c>
+      <c r="C256" s="16">
+        <v>23945</v>
+      </c>
+      <c r="D256" s="27" t="s">
+        <v>285</v>
+      </c>
+      <c r="E256" s="9">
+        <v>1480000000</v>
+      </c>
+      <c r="F256" s="9">
+        <v>101000000</v>
+      </c>
+      <c r="G256" s="9">
+        <v>151000000</v>
+      </c>
+      <c r="H256" s="9">
+        <v>0</v>
+      </c>
+      <c r="I256" s="9">
+        <v>447470000</v>
+      </c>
+      <c r="J256" s="10">
+        <v>141000000</v>
+      </c>
+      <c r="K256" s="9">
+        <v>0</v>
+      </c>
+      <c r="L256" s="9">
+        <v>0</v>
+      </c>
+      <c r="M256" s="9">
+        <v>617910000</v>
+      </c>
+      <c r="N256" s="9">
+        <v>460000000</v>
+      </c>
+      <c r="O256" s="9">
+        <v>55000000</v>
+      </c>
+      <c r="P256" s="9">
+        <v>30000000</v>
+      </c>
+      <c r="Q256" s="9">
+        <v>3483380000</v>
+      </c>
+      <c r="R256" s="8">
+        <v>1740031366.21</v>
+      </c>
+      <c r="S256" s="8">
+        <v>176225591</v>
+      </c>
+      <c r="T256" s="8">
+        <v>112517182</v>
+      </c>
+      <c r="U256" s="8">
+        <v>288677275</v>
+      </c>
+      <c r="V256" s="8">
+        <v>766656748</v>
+      </c>
+      <c r="W256" s="8">
+        <v>116310000.1336</v>
+      </c>
+      <c r="X256" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y256" s="8">
+        <v>1435924564</v>
+      </c>
+      <c r="Z256" s="8">
+        <v>71214567.07062</v>
+      </c>
+      <c r="AA256" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB256" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC256" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD256" s="11">
+        <v>4707557293.4142199</v>
+      </c>
+      <c r="AE256" s="25">
+        <v>1.6020000000000001</v>
+      </c>
+    </row>
+    <row r="257" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A257" s="23">
+        <v>256</v>
+      </c>
+      <c r="B257" s="13">
+        <v>27340</v>
+      </c>
+      <c r="C257" s="13">
+        <v>24071</v>
+      </c>
+      <c r="D257" s="26" t="s">
+        <v>286</v>
+      </c>
+      <c r="E257" s="9">
+        <v>77410200</v>
+      </c>
+      <c r="F257" s="9">
+        <v>11295570</v>
+      </c>
+      <c r="G257" s="9">
+        <v>3791520</v>
+      </c>
+      <c r="H257" s="9">
+        <v>0</v>
+      </c>
+      <c r="I257" s="9">
+        <v>35545500</v>
+      </c>
+      <c r="J257" s="10">
+        <v>7899000</v>
+      </c>
+      <c r="K257" s="9">
+        <v>0</v>
+      </c>
+      <c r="L257" s="9">
+        <v>1737780</v>
+      </c>
+      <c r="M257" s="9">
+        <v>1737780</v>
+      </c>
+      <c r="N257" s="9">
+        <v>9004860</v>
+      </c>
+      <c r="O257" s="9">
+        <v>0</v>
+      </c>
+      <c r="P257" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q257" s="9">
+        <v>148422210</v>
+      </c>
+      <c r="R257" s="8">
+        <v>0</v>
+      </c>
+      <c r="S257" s="8">
+        <v>1713273</v>
+      </c>
+      <c r="T257" s="8">
+        <v>7018182</v>
+      </c>
+      <c r="U257" s="8">
+        <v>0</v>
+      </c>
+      <c r="V257" s="8">
+        <v>20950287</v>
+      </c>
+      <c r="W257" s="8">
+        <v>1429751</v>
+      </c>
+      <c r="X257" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y257" s="8">
+        <v>15786363</v>
+      </c>
+      <c r="Z257" s="8">
+        <v>11665450.02465</v>
+      </c>
+      <c r="AA257" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB257" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC257" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD257" s="11">
+        <v>58563306.02465</v>
+      </c>
+      <c r="AE257" s="14">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="258" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A258" s="23">
+        <v>257</v>
+      </c>
+      <c r="B258" s="16">
+        <v>28023</v>
+      </c>
+      <c r="C258" s="16">
+        <v>24283</v>
+      </c>
+      <c r="D258" s="27" t="s">
+        <v>287</v>
+      </c>
+      <c r="E258" s="9">
+        <v>0</v>
+      </c>
+      <c r="F258" s="9">
+        <v>383008560</v>
+      </c>
+      <c r="G258" s="9">
+        <v>574512840</v>
+      </c>
+      <c r="H258" s="9">
+        <v>0</v>
+      </c>
+      <c r="I258" s="9">
+        <v>1196909736</v>
+      </c>
+      <c r="J258" s="10">
+        <v>191504280</v>
+      </c>
+      <c r="K258" s="9">
+        <v>0</v>
+      </c>
+      <c r="L258" s="9">
+        <v>95752140</v>
+      </c>
+      <c r="M258" s="9">
+        <v>1263265410</v>
+      </c>
+      <c r="N258" s="9">
+        <v>84252300</v>
+      </c>
+      <c r="O258" s="9">
+        <v>0</v>
+      </c>
+      <c r="P258" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q258" s="9">
+        <v>3789205266</v>
+      </c>
+      <c r="R258" s="8">
+        <v>0</v>
+      </c>
+      <c r="S258" s="8">
+        <v>146060355.375</v>
+      </c>
+      <c r="T258" s="8">
+        <v>556845127</v>
+      </c>
+      <c r="U258" s="8">
+        <v>503761669</v>
+      </c>
+      <c r="V258" s="8">
+        <v>468476019</v>
+      </c>
+      <c r="W258" s="8">
+        <v>55066657</v>
+      </c>
+      <c r="X258" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y258" s="8">
+        <v>997542856</v>
+      </c>
+      <c r="Z258" s="8">
+        <v>147603050.05125001</v>
+      </c>
+      <c r="AA258" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB258" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC258" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD258" s="11">
+        <v>2875355733.42625</v>
+      </c>
+      <c r="AE258" s="18">
+        <v>0.77600000000000002</v>
+      </c>
+    </row>
+    <row r="259" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A259" s="23">
+        <v>258</v>
+      </c>
+      <c r="B259" s="13">
+        <v>28165</v>
+      </c>
+      <c r="C259" s="13">
+        <v>24353</v>
+      </c>
+      <c r="D259" s="26" t="s">
+        <v>288</v>
+      </c>
+      <c r="E259" s="9">
+        <v>0</v>
+      </c>
+      <c r="F259" s="9">
+        <v>58986387</v>
+      </c>
+      <c r="G259" s="9">
+        <v>147477942</v>
+      </c>
+      <c r="H259" s="9">
+        <v>0</v>
+      </c>
+      <c r="I259" s="9">
+        <v>176967144</v>
+      </c>
+      <c r="J259" s="10">
+        <v>29489202</v>
+      </c>
+      <c r="K259" s="9">
+        <v>0</v>
+      </c>
+      <c r="L259" s="9">
+        <v>0</v>
+      </c>
+      <c r="M259" s="9">
+        <v>322640928</v>
+      </c>
+      <c r="N259" s="9">
+        <v>0</v>
+      </c>
+      <c r="O259" s="9">
+        <v>0</v>
+      </c>
+      <c r="P259" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q259" s="9">
+        <v>735561603</v>
+      </c>
+      <c r="R259" s="8">
+        <v>0</v>
+      </c>
+      <c r="S259" s="8">
+        <v>27292046</v>
+      </c>
+      <c r="T259" s="8">
+        <v>490909</v>
+      </c>
+      <c r="U259" s="8">
+        <v>0</v>
+      </c>
+      <c r="V259" s="8">
+        <v>378382651</v>
+      </c>
+      <c r="W259" s="8">
+        <v>61267558</v>
+      </c>
+      <c r="X259" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y259" s="8">
+        <v>56562928.5</v>
+      </c>
+      <c r="Z259" s="8">
+        <v>33577061.565729998</v>
+      </c>
+      <c r="AA259" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB259" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC259" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD259" s="11">
+        <v>557573154.06572998</v>
+      </c>
+      <c r="AE259" s="18">
+        <v>0.75800000000000001</v>
+      </c>
+    </row>
+    <row r="260" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A260" s="23">
+        <v>259</v>
+      </c>
+      <c r="B260" s="16">
+        <v>27952</v>
+      </c>
+      <c r="C260" s="16">
+        <v>24377</v>
+      </c>
+      <c r="D260" s="27" t="s">
+        <v>289</v>
+      </c>
+      <c r="E260" s="9">
+        <v>323202468</v>
+      </c>
+      <c r="F260" s="9">
+        <v>72211041</v>
+      </c>
+      <c r="G260" s="9">
+        <v>108316561</v>
+      </c>
+      <c r="H260" s="9">
+        <v>0</v>
+      </c>
+      <c r="I260" s="9">
+        <v>1083165850</v>
+      </c>
+      <c r="J260" s="10">
+        <v>72211041</v>
+      </c>
+      <c r="K260" s="9">
+        <v>0</v>
+      </c>
+      <c r="L260" s="9">
+        <v>144422081</v>
+      </c>
+      <c r="M260" s="9">
+        <v>1314193748</v>
+      </c>
+      <c r="N260" s="9">
+        <v>0</v>
+      </c>
+      <c r="O260" s="9">
+        <v>7908120</v>
+      </c>
+      <c r="P260" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q260" s="9">
+        <v>3125630910</v>
+      </c>
+      <c r="R260" s="8">
+        <v>496433385.86000001</v>
+      </c>
+      <c r="S260" s="8">
+        <v>36838136</v>
+      </c>
+      <c r="T260" s="8">
+        <v>89035171</v>
+      </c>
+      <c r="U260" s="8">
+        <v>78727272</v>
+      </c>
+      <c r="V260" s="8">
+        <v>116556068</v>
+      </c>
+      <c r="W260" s="8">
+        <v>23623481</v>
+      </c>
+      <c r="X260" s="8">
+        <v>22370139.440000001</v>
+      </c>
+      <c r="Y260" s="8">
+        <v>513072614</v>
+      </c>
+      <c r="Z260" s="8">
+        <v>143953719.66622001</v>
+      </c>
+      <c r="AA260" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB260" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC260" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD260" s="11">
+        <v>1520609986.9662201</v>
+      </c>
+      <c r="AE260" s="14">
+        <v>0.48799999999999999</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AI244">
-    <filterColumn colId="30">
-      <colorFilter dxfId="0"/>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AF244" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="C245:C260">
+    <cfRule type="duplicateValues" dxfId="0" priority="1" stopIfTrue="1"/>
+  </conditionalFormatting>
   <printOptions gridLines="1" gridLinesSet="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup paperSize="0" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
